--- a/data/tabys_instruments.xlsx
+++ b/data/tabys_instruments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,22 +519,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KZX000002241</t>
+          <t>KZX000000526</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SOLV3.0526</t>
+          <t>IXG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>iX</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solva Group Limited</t>
+          <t>iX Gold SPC Limited</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -553,7 +553,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Deleted</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -562,28 +566,176 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>iX Gold</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2030-10-05T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KZX000001086</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IXI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>iX</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>iX Islamic SPC Ltd</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Deleted</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>IX Islamic ETN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2032-06-03T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>KZX000002241</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SOLV3.0526</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SOLV</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solva Group Limited</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Coupon bonds of Solva Group Ltd</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2026-05-27T00:00:00Z</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="P4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
